--- a/output/Data and Chart Outputs/taiwan_taipower.xlsx
+++ b/output/Data and Chart Outputs/taiwan_taipower.xlsx
@@ -1007,7 +1007,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -1068,6 +1068,91 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>Incremental: the committed workbook is the history store. The 10-minute file is downloaded (about 200 MB) only when its window ends after the last stored day; days with all 144 stamps are added. History starts with the first window available at the first run.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>FUEL MAPPING (Taipower FUEL_TYPE label -&gt; column)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>太陽能 -&gt; Solar</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>抽蓄發電 -&gt; Pumped_storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>抽蓄電 -&gt; Pumped_storage</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>核能 -&gt; Nuclear</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>水力 -&gt; Hydro</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>汽電共生 -&gt; Cogeneration</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>燃氣 -&gt; Gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>燃油 -&gt; Oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>燃煤 -&gt; Coal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>輕油 -&gt; Oil</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>風力 -&gt; Wind</t>
         </is>
       </c>
     </row>
@@ -19784,7 +19869,7 @@
         <v>671.5</v>
       </c>
       <c r="K5" t="n">
-        <v>411318.6</v>
+        <v>411318.7</v>
       </c>
     </row>
     <row r="6">
@@ -19819,7 +19904,7 @@
         <v>417.1</v>
       </c>
       <c r="K6" t="n">
-        <v>439393.9</v>
+        <v>439393.8</v>
       </c>
     </row>
     <row r="7">
@@ -20029,7 +20114,7 @@
         <v>1552.7</v>
       </c>
       <c r="K12" t="n">
-        <v>368266.2</v>
+        <v>368266.1</v>
       </c>
     </row>
     <row r="13">
@@ -20099,7 +20184,7 @@
         <v>1510.5</v>
       </c>
       <c r="K14" t="n">
-        <v>352911.9</v>
+        <v>352912</v>
       </c>
     </row>
     <row r="15">
@@ -20134,7 +20219,7 @@
         <v>1414.9</v>
       </c>
       <c r="K15" t="n">
-        <v>332235.6</v>
+        <v>332235.8</v>
       </c>
     </row>
     <row r="16">
@@ -20169,7 +20254,7 @@
         <v>1354.1</v>
       </c>
       <c r="K16" t="n">
-        <v>348177.1</v>
+        <v>348176.9</v>
       </c>
     </row>
     <row r="17">
@@ -20274,7 +20359,7 @@
         <v>1302</v>
       </c>
       <c r="K19" t="n">
-        <v>395029.1</v>
+        <v>395029.2</v>
       </c>
     </row>
     <row r="20">
@@ -20309,7 +20394,7 @@
         <v>1209.6</v>
       </c>
       <c r="K20" t="n">
-        <v>373282.5</v>
+        <v>373282.3</v>
       </c>
     </row>
     <row r="21">
@@ -20449,7 +20534,7 @@
         <v>504.9</v>
       </c>
       <c r="K24" t="n">
-        <v>403899.6</v>
+        <v>403899.7</v>
       </c>
     </row>
     <row r="25">
@@ -20484,7 +20569,7 @@
         <v>304</v>
       </c>
       <c r="K25" t="n">
-        <v>433257.5</v>
+        <v>433257.4</v>
       </c>
     </row>
     <row r="26">
@@ -20519,7 +20604,7 @@
         <v>524.7</v>
       </c>
       <c r="K26" t="n">
-        <v>405477.9</v>
+        <v>405477.8</v>
       </c>
     </row>
     <row r="27">
@@ -20554,7 +20639,7 @@
         <v>1102.5</v>
       </c>
       <c r="K27" t="n">
-        <v>390678.6</v>
+        <v>390678.4</v>
       </c>
     </row>
     <row r="28">
@@ -20589,7 +20674,7 @@
         <v>998.5</v>
       </c>
       <c r="K28" t="n">
-        <v>396745.1</v>
+        <v>396745.2</v>
       </c>
     </row>
     <row r="29">
@@ -20624,7 +20709,7 @@
         <v>1111.6</v>
       </c>
       <c r="K29" t="n">
-        <v>330790.3</v>
+        <v>330790.2</v>
       </c>
     </row>
     <row r="30">
@@ -20694,7 +20779,7 @@
         <v>1173.1</v>
       </c>
       <c r="K31" t="n">
-        <v>381319.9</v>
+        <v>381320</v>
       </c>
     </row>
     <row r="32">
@@ -20729,7 +20814,7 @@
         <v>1221.5</v>
       </c>
       <c r="K32" t="n">
-        <v>395899</v>
+        <v>395899.1</v>
       </c>
     </row>
     <row r="33">
@@ -20740,31 +20825,31 @@
         <v>0</v>
       </c>
       <c r="C33" t="n">
-        <v>14468.7</v>
+        <v>7234.3</v>
       </c>
       <c r="D33" t="n">
-        <v>310940.8</v>
+        <v>155470.4</v>
       </c>
       <c r="E33" t="n">
-        <v>46279.6</v>
+        <v>23139.8</v>
       </c>
       <c r="F33" t="n">
-        <v>448282.2</v>
+        <v>224141.1</v>
       </c>
       <c r="G33" t="n">
-        <v>25461.9</v>
+        <v>12730.9</v>
       </c>
       <c r="H33" t="n">
-        <v>9174.4</v>
+        <v>4587.2</v>
       </c>
       <c r="I33" t="n">
-        <v>5326</v>
+        <v>2663</v>
       </c>
       <c r="J33" t="n">
-        <v>878.5</v>
+        <v>439.3</v>
       </c>
       <c r="K33" t="n">
-        <v>846343.4</v>
+        <v>423171.7</v>
       </c>
     </row>
     <row r="34">
@@ -20799,7 +20884,7 @@
         <v>993.2</v>
       </c>
       <c r="K34" t="n">
-        <v>378793.5</v>
+        <v>378793.4</v>
       </c>
     </row>
     <row r="35">
@@ -20834,7 +20919,7 @@
         <v>1058.6</v>
       </c>
       <c r="K35" t="n">
-        <v>396921.6</v>
+        <v>396921.5</v>
       </c>
     </row>
     <row r="36">
@@ -20939,7 +21024,7 @@
         <v>451.7</v>
       </c>
       <c r="K38" t="n">
-        <v>385311.8</v>
+        <v>385311.7</v>
       </c>
     </row>
     <row r="39">
@@ -20974,7 +21059,7 @@
         <v>392.6</v>
       </c>
       <c r="K39" t="n">
-        <v>427399.6</v>
+        <v>427399.7</v>
       </c>
     </row>
     <row r="40">
@@ -21009,7 +21094,7 @@
         <v>575.8</v>
       </c>
       <c r="K40" t="n">
-        <v>431179.7</v>
+        <v>431179.6</v>
       </c>
     </row>
     <row r="41">
@@ -21044,7 +21129,7 @@
         <v>1121.7</v>
       </c>
       <c r="K41" t="n">
-        <v>443165.3</v>
+        <v>443165.4</v>
       </c>
     </row>
     <row r="42">
@@ -21149,7 +21234,7 @@
         <v>1311.2</v>
       </c>
       <c r="K44" t="n">
-        <v>413597.9</v>
+        <v>413598</v>
       </c>
     </row>
     <row r="45">
@@ -21184,7 +21269,7 @@
         <v>1338.7</v>
       </c>
       <c r="K45" t="n">
-        <v>433459.2</v>
+        <v>433459.3</v>
       </c>
     </row>
     <row r="46">
@@ -21219,7 +21304,7 @@
         <v>1262.1</v>
       </c>
       <c r="K46" t="n">
-        <v>443793.5</v>
+        <v>443793.6</v>
       </c>
     </row>
     <row r="47">
@@ -21254,7 +21339,7 @@
         <v>652.6</v>
       </c>
       <c r="K47" t="n">
-        <v>469977</v>
+        <v>469976.9</v>
       </c>
     </row>
     <row r="48">
@@ -21394,7 +21479,7 @@
         <v>1307.9</v>
       </c>
       <c r="K51" t="n">
-        <v>398938.4</v>
+        <v>398938.5</v>
       </c>
     </row>
     <row r="52">
@@ -21499,7 +21584,7 @@
         <v>1247.8</v>
       </c>
       <c r="K54" t="n">
-        <v>430416.4</v>
+        <v>430416.3</v>
       </c>
     </row>
     <row r="55">
@@ -21639,7 +21724,7 @@
         <v>1443.8</v>
       </c>
       <c r="K58" t="n">
-        <v>367609.6</v>
+        <v>367609.7</v>
       </c>
     </row>
     <row r="59">
@@ -21709,7 +21794,7 @@
         <v>945.2</v>
       </c>
       <c r="K60" t="n">
-        <v>434582.4</v>
+        <v>434582.3</v>
       </c>
     </row>
     <row r="61">
@@ -21779,7 +21864,7 @@
         <v>534</v>
       </c>
       <c r="K62" t="n">
-        <v>347528.6</v>
+        <v>347528.5</v>
       </c>
     </row>
     <row r="63">
@@ -21814,7 +21899,7 @@
         <v>1108.4</v>
       </c>
       <c r="K63" t="n">
-        <v>311876.6</v>
+        <v>311876.7</v>
       </c>
     </row>
     <row r="64">
@@ -21884,7 +21969,7 @@
         <v>1243.3</v>
       </c>
       <c r="K65" t="n">
-        <v>352409.1</v>
+        <v>352409</v>
       </c>
     </row>
     <row r="66">
@@ -21919,7 +22004,7 @@
         <v>1095.4</v>
       </c>
       <c r="K66" t="n">
-        <v>332821.2</v>
+        <v>332821.1</v>
       </c>
     </row>
     <row r="67">
@@ -22024,7 +22109,7 @@
         <v>1329.1</v>
       </c>
       <c r="K69" t="n">
-        <v>394837.7</v>
+        <v>394837.6</v>
       </c>
     </row>
     <row r="70">
@@ -22059,7 +22144,7 @@
         <v>1353.3</v>
       </c>
       <c r="K70" t="n">
-        <v>367450.3</v>
+        <v>367450.4</v>
       </c>
     </row>
     <row r="71">
@@ -22094,7 +22179,7 @@
         <v>1315.8</v>
       </c>
       <c r="K71" t="n">
-        <v>306181.8</v>
+        <v>306181.7</v>
       </c>
     </row>
     <row r="72">
@@ -22129,7 +22214,7 @@
         <v>1180</v>
       </c>
       <c r="K72" t="n">
-        <v>322836.4</v>
+        <v>322836.3</v>
       </c>
     </row>
     <row r="73">
@@ -22164,7 +22249,7 @@
         <v>1183.2</v>
       </c>
       <c r="K73" t="n">
-        <v>383602.9</v>
+        <v>383603</v>
       </c>
     </row>
     <row r="74">
@@ -22199,7 +22284,7 @@
         <v>1305.9</v>
       </c>
       <c r="K74" t="n">
-        <v>391596.3</v>
+        <v>391596.2</v>
       </c>
     </row>
     <row r="75">
@@ -22269,7 +22354,7 @@
         <v>444.3</v>
       </c>
       <c r="K76" t="n">
-        <v>411612.2</v>
+        <v>411612.1</v>
       </c>
     </row>
     <row r="77">
@@ -22304,7 +22389,7 @@
         <v>1181.1</v>
       </c>
       <c r="K77" t="n">
-        <v>373831.6</v>
+        <v>373831.7</v>
       </c>
     </row>
     <row r="78">
@@ -22374,7 +22459,7 @@
         <v>1291</v>
       </c>
       <c r="K79" t="n">
-        <v>352220.3</v>
+        <v>352220.2</v>
       </c>
     </row>
     <row r="80">
@@ -22409,7 +22494,7 @@
         <v>1320</v>
       </c>
       <c r="K80" t="n">
-        <v>399193.3</v>
+        <v>399193.4</v>
       </c>
     </row>
     <row r="81">
@@ -22444,7 +22529,7 @@
         <v>1252.6</v>
       </c>
       <c r="K81" t="n">
-        <v>400607.7</v>
+        <v>400607.8</v>
       </c>
     </row>
     <row r="82">
@@ -22514,7 +22599,7 @@
         <v>973.6</v>
       </c>
       <c r="K83" t="n">
-        <v>456753.1</v>
+        <v>456753</v>
       </c>
     </row>
     <row r="84">
@@ -22584,7 +22669,7 @@
         <v>962.2</v>
       </c>
       <c r="K85" t="n">
-        <v>442041.9</v>
+        <v>442041.8</v>
       </c>
     </row>
     <row r="86">
@@ -22654,7 +22739,7 @@
         <v>1318.9</v>
       </c>
       <c r="K87" t="n">
-        <v>434931</v>
+        <v>434931.1</v>
       </c>
     </row>
     <row r="88">
@@ -22689,7 +22774,7 @@
         <v>1302.7</v>
       </c>
       <c r="K88" t="n">
-        <v>432028.9</v>
+        <v>432029</v>
       </c>
     </row>
     <row r="89">
@@ -22724,7 +22809,7 @@
         <v>1251.2</v>
       </c>
       <c r="K89" t="n">
-        <v>445116.1</v>
+        <v>445116</v>
       </c>
     </row>
     <row r="90">
@@ -22759,7 +22844,7 @@
         <v>1265.8</v>
       </c>
       <c r="K90" t="n">
-        <v>460644.8</v>
+        <v>460644.9</v>
       </c>
     </row>
     <row r="91">
@@ -22794,7 +22879,7 @@
         <v>1244</v>
       </c>
       <c r="K91" t="n">
-        <v>441427.4</v>
+        <v>441427.3</v>
       </c>
     </row>
     <row r="92">
@@ -22829,7 +22914,7 @@
         <v>1150.5</v>
       </c>
       <c r="K92" t="n">
-        <v>377072.6</v>
+        <v>377072.5</v>
       </c>
     </row>
     <row r="93">
@@ -22864,7 +22949,7 @@
         <v>1464.6</v>
       </c>
       <c r="K93" t="n">
-        <v>375343.5</v>
+        <v>375343.7</v>
       </c>
     </row>
   </sheetData>
